--- a/whitelist.xlsx
+++ b/whitelist.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F377"/>
+  <dimension ref="A1:F411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -11010,6 +11010,1026 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" s="5" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" s="5" t="inlineStr">
+        <is>
+          <t>kelio.art</t>
+        </is>
+      </c>
+      <c r="C378" s="5" t="inlineStr">
+        <is>
+          <t>Kelio企業管理軟體</t>
+        </is>
+      </c>
+      <c r="D378" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E378" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F378" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>career-nthu.conf.asia</t>
+        </is>
+      </c>
+      <c r="C379" s="3" t="inlineStr">
+        <is>
+          <t>清大職涯發展中心</t>
+        </is>
+      </c>
+      <c r="D379" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E379" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F379" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" s="5" t="inlineStr">
+        <is>
+          <t>blog.twshop.asia</t>
+        </is>
+      </c>
+      <c r="C380" s="5" t="inlineStr">
+        <is>
+          <t>TWShop購物部落格</t>
+        </is>
+      </c>
+      <c r="D380" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E380" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F380" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="3" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
+          <t>greatgame.asia</t>
+        </is>
+      </c>
+      <c r="C381" s="3" t="inlineStr">
+        <is>
+          <t>GreatGame亞洲遊戲平台</t>
+        </is>
+      </c>
+      <c r="D381" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E381" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F381" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="5" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" s="5" t="inlineStr">
+        <is>
+          <t>drg.best</t>
+        </is>
+      </c>
+      <c r="C382" s="5" t="inlineStr">
+        <is>
+          <t>DRG數位資源組</t>
+        </is>
+      </c>
+      <c r="D382" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E382" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F382" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="3" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>bbshwp.best</t>
+        </is>
+      </c>
+      <c r="C383" s="3" t="inlineStr">
+        <is>
+          <t>bbshwp（非JX，Dynadot近期）</t>
+        </is>
+      </c>
+      <c r="D383" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E383" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F383" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="5" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" s="5" t="inlineStr">
+        <is>
+          <t>ptt.cc</t>
+        </is>
+      </c>
+      <c r="C384" s="5" t="inlineStr">
+        <is>
+          <t>PTT批踢踢實業坊</t>
+        </is>
+      </c>
+      <c r="D384" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E384" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F384" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="3" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" s="3" t="inlineStr">
+        <is>
+          <t>dcmath.cc</t>
+        </is>
+      </c>
+      <c r="C385" s="3" t="inlineStr">
+        <is>
+          <t>DC數學教育</t>
+        </is>
+      </c>
+      <c r="D385" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E385" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F385" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="5" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" s="5" t="inlineStr">
+        <is>
+          <t>disp.cc</t>
+        </is>
+      </c>
+      <c r="C386" s="5" t="inlineStr">
+        <is>
+          <t>Disp BBS討論板</t>
+        </is>
+      </c>
+      <c r="D386" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E386" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F386" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="3" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>ppt.cc</t>
+        </is>
+      </c>
+      <c r="C387" s="3" t="inlineStr">
+        <is>
+          <t>PPT簡報工具</t>
+        </is>
+      </c>
+      <c r="D387" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E387" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F387" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="5" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" s="5" t="inlineStr">
+        <is>
+          <t>timmyblog.cc</t>
+        </is>
+      </c>
+      <c r="C388" s="5" t="inlineStr">
+        <is>
+          <t>Timmy個人部落格</t>
+        </is>
+      </c>
+      <c r="D388" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E388" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F388" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="3" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" s="3" t="inlineStr">
+        <is>
+          <t>scitw.cc</t>
+        </is>
+      </c>
+      <c r="C389" s="3" t="inlineStr">
+        <is>
+          <t>科學月刊台灣</t>
+        </is>
+      </c>
+      <c r="D389" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E389" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F389" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="5" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" s="5" t="inlineStr">
+        <is>
+          <t>nubaby.cc</t>
+        </is>
+      </c>
+      <c r="C390" s="5" t="inlineStr">
+        <is>
+          <t>NuBaby親子資訊站</t>
+        </is>
+      </c>
+      <c r="D390" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E390" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F390" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="3" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" s="3" t="inlineStr">
+        <is>
+          <t>energy.nuu.cloud</t>
+        </is>
+      </c>
+      <c r="C391" s="3" t="inlineStr">
+        <is>
+          <t>聯合大學能源工程系</t>
+        </is>
+      </c>
+      <c r="D391" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F391" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="5" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" s="5" t="inlineStr">
+        <is>
+          <t>tianya-book.cloud</t>
+        </is>
+      </c>
+      <c r="C392" s="5" t="inlineStr">
+        <is>
+          <t>天涯書庫</t>
+        </is>
+      </c>
+      <c r="D392" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E392" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F392" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="3" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" s="3" t="inlineStr">
+        <is>
+          <t>opentix.life</t>
+        </is>
+      </c>
+      <c r="C393" s="3" t="inlineStr">
+        <is>
+          <t>OpenTix開放式票務系統</t>
+        </is>
+      </c>
+      <c r="D393" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E393" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F393" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="5" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" s="5" t="inlineStr">
+        <is>
+          <t>goodjob.life</t>
+        </is>
+      </c>
+      <c r="C394" s="5" t="inlineStr">
+        <is>
+          <t>GoodJob職場透明化運動</t>
+        </is>
+      </c>
+      <c r="D394" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E394" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F394" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="3" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" s="3" t="inlineStr">
+        <is>
+          <t>media.goodjob.life</t>
+        </is>
+      </c>
+      <c r="C395" s="3" t="inlineStr">
+        <is>
+          <t>GoodJob媒體子站</t>
+        </is>
+      </c>
+      <c r="D395" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E395" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F395" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="5" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" s="5" t="inlineStr">
+        <is>
+          <t>yaoen.live</t>
+        </is>
+      </c>
+      <c r="C396" s="5" t="inlineStr">
+        <is>
+          <t>瑤恩直播/媒體站</t>
+        </is>
+      </c>
+      <c r="D396" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E396" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F396" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="3" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" s="3" t="inlineStr">
+        <is>
+          <t>goldenapple.media</t>
+        </is>
+      </c>
+      <c r="C397" s="3" t="inlineStr">
+        <is>
+          <t>GoldenApple媒體</t>
+        </is>
+      </c>
+      <c r="D397" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E397" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F397" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="5" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" s="5" t="inlineStr">
+        <is>
+          <t>partystar.media</t>
+        </is>
+      </c>
+      <c r="C398" s="5" t="inlineStr">
+        <is>
+          <t>PartyStar活動媒體</t>
+        </is>
+      </c>
+      <c r="D398" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E398" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F398" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="3" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" s="3" t="inlineStr">
+        <is>
+          <t>ipad-fix.mobi</t>
+        </is>
+      </c>
+      <c r="C399" s="3" t="inlineStr">
+        <is>
+          <t>iPad維修服務站</t>
+        </is>
+      </c>
+      <c r="D399" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E399" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F399" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="5" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" s="5" t="inlineStr">
+        <is>
+          <t>grwth.mobi</t>
+        </is>
+      </c>
+      <c r="C400" s="5" t="inlineStr">
+        <is>
+          <t>GRWTH學習成長平台</t>
+        </is>
+      </c>
+      <c r="D400" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E400" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F400" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" s="3" t="inlineStr">
+        <is>
+          <t>fsl.onl</t>
+        </is>
+      </c>
+      <c r="C401" s="3" t="inlineStr">
+        <is>
+          <t>FSL線上平台</t>
+        </is>
+      </c>
+      <c r="D401" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E401" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F401" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="5" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" s="5" t="inlineStr">
+        <is>
+          <t>luckywater.space</t>
+        </is>
+      </c>
+      <c r="C402" s="5" t="inlineStr">
+        <is>
+          <t>幸運水空間設計</t>
+        </is>
+      </c>
+      <c r="D402" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E402" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F402" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="3" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
+        <is>
+          <t>ponycanyon.us</t>
+        </is>
+      </c>
+      <c r="C403" s="3" t="inlineStr">
+        <is>
+          <t>Pony Canyon美國官網</t>
+        </is>
+      </c>
+      <c r="D403" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E403" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F403" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="5" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" s="5" t="inlineStr">
+        <is>
+          <t>overcomingchurch.us</t>
+        </is>
+      </c>
+      <c r="C404" s="5" t="inlineStr">
+        <is>
+          <t>美國教會網站</t>
+        </is>
+      </c>
+      <c r="D404" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E404" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F404" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
+          <t>k4j.us</t>
+        </is>
+      </c>
+      <c r="C405" s="3" t="inlineStr">
+        <is>
+          <t>K4J美國站</t>
+        </is>
+      </c>
+      <c r="D405" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E405" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F405" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="5" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" s="5" t="inlineStr">
+        <is>
+          <t>qmtw.us</t>
+        </is>
+      </c>
+      <c r="C406" s="5" t="inlineStr">
+        <is>
+          <t>QMTW美國站</t>
+        </is>
+      </c>
+      <c r="D406" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E406" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F406" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="3" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>chris-studio.work</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="inlineStr">
+        <is>
+          <t>Chris設計工作室</t>
+        </is>
+      </c>
+      <c r="D407" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E407" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F407" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="5" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" s="5" t="inlineStr">
+        <is>
+          <t>kiddotask.xyz</t>
+        </is>
+      </c>
+      <c r="C408" s="5" t="inlineStr">
+        <is>
+          <t>KiddoTask兒童任務APP</t>
+        </is>
+      </c>
+      <c r="D408" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E408" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F408" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="3" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>help.autopass.xyz</t>
+        </is>
+      </c>
+      <c r="C409" s="3" t="inlineStr">
+        <is>
+          <t>AutoPass客服站</t>
+        </is>
+      </c>
+      <c r="D409" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E409" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F409" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="5" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" s="5" t="inlineStr">
+        <is>
+          <t>standuploser.xyz</t>
+        </is>
+      </c>
+      <c r="C410" s="5" t="inlineStr">
+        <is>
+          <t>StandUpLoser單口喜劇站</t>
+        </is>
+      </c>
+      <c r="D410" s="5" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E410" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F410" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="3" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" s="3" t="inlineStr">
+        <is>
+          <t>papacat.xyz</t>
+        </is>
+      </c>
+      <c r="C411" s="3" t="inlineStr">
+        <is>
+          <t>PapaCat個人站</t>
+        </is>
+      </c>
+      <c r="D411" s="3" t="inlineStr">
+        <is>
+          <t>0613</t>
+        </is>
+      </c>
+      <c r="E411" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F411" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
